--- a/九龙-九龙塘-喇沙汇/喇沙汇_销控明细表.xlsx
+++ b/九龙-九龙塘-喇沙汇/喇沙汇_销控明细表.xlsx
@@ -200,61 +200,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -640,6 +640,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -697,6 +701,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -743,6 +767,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -789,6 +833,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -835,6 +899,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -881,13 +965,33 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/九龙-九龙塘-喇沙汇/喇沙汇_销控明细表.xlsx
+++ b/九龙-九龙塘-喇沙汇/喇沙汇_销控明细表.xlsx
@@ -116,8 +116,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -259,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -636,7 +635,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -751,19 +750,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>187910000</v>
+        <v>420000899</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>36480</v>
+        <v>81538</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -817,19 +816,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>208012000</v>
+        <v>420000899</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>39314</v>
+        <v>79380</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -883,19 +882,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>166060000</v>
+        <v>420000899</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>34603</v>
+        <v>87518</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -949,19 +948,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>170430000</v>
+        <v>420000899</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>34500</v>
+        <v>85020</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1071,12 +1070,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -1122,18 +1121,18 @@
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>A2 | 5291呎 (4+房)
-$20801万
-$39,314/呎
-(暂停销售)</t>
+$42000万
+$79,380/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr"/>
       <c r="E5" s="21" t="inlineStr">
         <is>
           <t>B2 | 5151呎 (4+房)
-$18791万
-$36,480/呎
-(暂停销售)</t>
+$42000万
+$81,538/呎
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -1146,18 +1145,18 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A1 | 4940呎 (4+房)
-$17043万
-$34,500/呎
-(暂停销售)</t>
+$42000万
+$85,020/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t>B1 | 4799呎 (4+房)
-$16606万
-$34,603/呎
-(暂停销售)</t>
+$42000万
+$87,518/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
